--- a/jogos_2025-07-01.xlsx
+++ b/jogos_2025-07-01.xlsx
@@ -804,34 +804,34 @@
         <v>2.8</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
         <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AA2">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AB2">
         <v>1.67</v>
@@ -840,22 +840,22 @@
         <v>2</v>
       </c>
       <c r="AD2">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AE2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF2">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AG2">
         <v>2</v>
       </c>
       <c r="AH2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AI2">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ2" t="s">
         <v>66</v>
@@ -864,46 +864,46 @@
         <v>66</v>
       </c>
       <c r="AL2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM2">
         <v>1.23</v>
       </c>
       <c r="AN2">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AO2">
         <v>-1</v>
       </c>
       <c r="AP2">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AR2">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AS2">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AT2">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="AU2">
-        <v>4.55</v>
+        <v>3.45</v>
       </c>
       <c r="AV2">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AW2">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AX2">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AY2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -974,58 +974,58 @@
         <v>3.1</v>
       </c>
       <c r="R3">
+        <v>1.35</v>
+      </c>
+      <c r="S3">
+        <v>2.85</v>
+      </c>
+      <c r="T3">
+        <v>2.5</v>
+      </c>
+      <c r="U3">
+        <v>1.45</v>
+      </c>
+      <c r="V3">
+        <v>5.8</v>
+      </c>
+      <c r="W3">
+        <v>1.1</v>
+      </c>
+      <c r="X3">
+        <v>1.04</v>
+      </c>
+      <c r="Y3">
+        <v>10</v>
+      </c>
+      <c r="Z3">
+        <v>1.22</v>
+      </c>
+      <c r="AA3">
+        <v>3.75</v>
+      </c>
+      <c r="AB3">
+        <v>1.7</v>
+      </c>
+      <c r="AC3">
+        <v>1.95</v>
+      </c>
+      <c r="AD3">
+        <v>2.9</v>
+      </c>
+      <c r="AE3">
         <v>1.36</v>
       </c>
-      <c r="S3">
-        <v>3</v>
-      </c>
-      <c r="T3">
-        <v>2.63</v>
-      </c>
-      <c r="U3">
-        <v>1.44</v>
-      </c>
-      <c r="V3">
-        <v>6</v>
-      </c>
-      <c r="W3">
-        <v>1.11</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>1.8</v>
-      </c>
-      <c r="AC3">
-        <v>2</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
       <c r="AF3">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ3" t="s">
         <v>66</v>
@@ -1034,46 +1034,46 @@
         <v>66</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ3">
         <v>0</v>

--- a/jogos_2025-07-01.xlsx
+++ b/jogos_2025-07-01.xlsx
@@ -804,58 +804,58 @@
         <v>2.8</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U2">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V2">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>13.9</v>
       </c>
       <c r="Z2">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AA2">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="AB2">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AC2">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD2">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AE2">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AF2">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH2">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AI2">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
         <v>66</v>
@@ -870,40 +870,40 @@
         <v>1.23</v>
       </c>
       <c r="AN2">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="AO2">
         <v>-1</v>
       </c>
       <c r="AP2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AQ2">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AS2">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AT2">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AU2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AV2">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AW2">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AX2">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AY2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -974,34 +974,34 @@
         <v>3.1</v>
       </c>
       <c r="R3">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S3">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="T3">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U3">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V3">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W3">
         <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AA3">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB3">
         <v>1.7</v>
@@ -1010,16 +1010,16 @@
         <v>1.95</v>
       </c>
       <c r="AD3">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AE3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH3">
         <v>5.5</v>
@@ -1034,46 +1034,46 @@
         <v>66</v>
       </c>
       <c r="AL3">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AQ3">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AR3">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AS3">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AT3">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="AU3">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="AV3">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AW3">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AX3">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AY3">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AZ3">
         <v>0</v>

--- a/jogos_2025-07-01.xlsx
+++ b/jogos_2025-07-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -127,69 +127,21 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
+    <t>11:00</t>
+  </si>
+  <si>
     <t>12:00</t>
   </si>
   <si>
     <t>16:00</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
@@ -199,12 +151,18 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Colón</t>
+  </si>
+  <si>
     <t>KuPS</t>
   </si>
   <si>
     <t>HFX Wanderers FC</t>
   </si>
   <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
@@ -214,7 +172,22 @@
     <t>incomplete</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['41', '37', '45+1', '51', '80', '64']</t>
+  </si>
+  <si>
+    <t>['67', '84', '86']</t>
+  </si>
+  <si>
+    <t>['16', '47']</t>
+  </si>
+  <si>
+    <t>['19']</t>
   </si>
 </sst>
 </file>
@@ -578,10 +551,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD3"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,79 +669,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45839</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -783,311 +702,319 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L2">
-        <v>1.58</v>
+        <v>2.13</v>
       </c>
       <c r="M2">
-        <v>3.72</v>
+        <v>2.61</v>
       </c>
       <c r="N2">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="O2">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="P2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="S2">
-        <v>3.42</v>
+        <v>2</v>
       </c>
       <c r="T2">
-        <v>2.25</v>
+        <v>5.1</v>
       </c>
       <c r="U2">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="V2">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
+        <v>1.16</v>
+      </c>
+      <c r="Y2">
+        <v>4.33</v>
+      </c>
+      <c r="Z2">
+        <v>1.7</v>
+      </c>
+      <c r="AA2">
+        <v>1.99</v>
+      </c>
+      <c r="AB2">
+        <v>3.5</v>
+      </c>
+      <c r="AC2">
+        <v>1.32</v>
+      </c>
+      <c r="AD2">
+        <v>7</v>
+      </c>
+      <c r="AE2">
         <v>1.03</v>
       </c>
-      <c r="Y2">
-        <v>13.9</v>
-      </c>
-      <c r="Z2">
-        <v>1.2</v>
-      </c>
-      <c r="AA2">
-        <v>4.6</v>
-      </c>
-      <c r="AB2">
-        <v>1.57</v>
-      </c>
-      <c r="AC2">
-        <v>2.25</v>
-      </c>
-      <c r="AD2">
-        <v>2.63</v>
-      </c>
-      <c r="AE2">
-        <v>1.51</v>
-      </c>
       <c r="AF2">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AG2">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="AH2">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="AI2">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="AK2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL2">
-        <v>1.25</v>
-      </c>
-      <c r="AM2">
-        <v>1.23</v>
-      </c>
-      <c r="AN2">
-        <v>2.3</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.24</v>
-      </c>
-      <c r="AQ2">
-        <v>1.29</v>
-      </c>
-      <c r="AR2">
-        <v>1.65</v>
-      </c>
-      <c r="AS2">
-        <v>1.99</v>
-      </c>
-      <c r="AT2">
-        <v>2.6</v>
-      </c>
-      <c r="AU2">
-        <v>3.55</v>
-      </c>
-      <c r="AV2">
-        <v>2.6</v>
-      </c>
-      <c r="AW2">
-        <v>2.21</v>
-      </c>
-      <c r="AX2">
-        <v>1.8</v>
-      </c>
-      <c r="AY2">
-        <v>1.48</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.51</v>
-      </c>
-      <c r="BC2">
-        <v>2.8</v>
-      </c>
-      <c r="BD2" s="3">
-        <v>45839.5</v>
+        <v>53</v>
+      </c>
+      <c r="AL2" s="3">
+        <v>45839.45833333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45839</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="L3">
         <v>1.6</v>
       </c>
       <c r="M3">
+        <v>3.9</v>
+      </c>
+      <c r="N3">
+        <v>5.11</v>
+      </c>
+      <c r="O3">
+        <v>1.51</v>
+      </c>
+      <c r="P3">
+        <v>11</v>
+      </c>
+      <c r="Q3">
+        <v>2.8</v>
+      </c>
+      <c r="R3">
+        <v>1.25</v>
+      </c>
+      <c r="S3">
+        <v>3.5</v>
+      </c>
+      <c r="T3">
+        <v>2.31</v>
+      </c>
+      <c r="U3">
+        <v>1.66</v>
+      </c>
+      <c r="V3">
+        <v>4.9</v>
+      </c>
+      <c r="W3">
+        <v>1.14</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>14.3</v>
+      </c>
+      <c r="Z3">
+        <v>1.15</v>
+      </c>
+      <c r="AA3">
+        <v>5</v>
+      </c>
+      <c r="AB3">
+        <v>1.53</v>
+      </c>
+      <c r="AC3">
+        <v>2.4</v>
+      </c>
+      <c r="AD3">
+        <v>2.4</v>
+      </c>
+      <c r="AE3">
+        <v>1.61</v>
+      </c>
+      <c r="AF3">
+        <v>1.62</v>
+      </c>
+      <c r="AG3">
+        <v>2.25</v>
+      </c>
+      <c r="AH3">
+        <v>4.59</v>
+      </c>
+      <c r="AI3">
+        <v>1.22</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL3" s="3">
+        <v>45839.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38">
+      <c r="A4" s="2">
+        <v>45839</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4">
+        <v>1.6</v>
+      </c>
+      <c r="M4">
         <v>3.8</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>4.5</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>1.44</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>0</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>3.1</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>1.32</v>
       </c>
-      <c r="S3">
+      <c r="S4">
         <v>2.95</v>
       </c>
-      <c r="T3">
+      <c r="T4">
         <v>2.55</v>
       </c>
-      <c r="U3">
+      <c r="U4">
         <v>1.42</v>
       </c>
-      <c r="V3">
-        <v>6.5</v>
-      </c>
-      <c r="W3">
-        <v>1.1</v>
-      </c>
-      <c r="X3">
+      <c r="V4">
+        <v>6.4</v>
+      </c>
+      <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
         <v>1.05</v>
       </c>
-      <c r="Y3">
-        <v>11</v>
-      </c>
-      <c r="Z3">
-        <v>1.19</v>
-      </c>
-      <c r="AA3">
-        <v>3.6</v>
-      </c>
-      <c r="AB3">
+      <c r="Y4">
+        <v>10</v>
+      </c>
+      <c r="Z4">
+        <v>1.23</v>
+      </c>
+      <c r="AA4">
+        <v>3.5</v>
+      </c>
+      <c r="AB4">
         <v>1.7</v>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <v>1.95</v>
       </c>
-      <c r="AD3">
-        <v>3</v>
-      </c>
-      <c r="AE3">
+      <c r="AD4">
+        <v>3.1</v>
+      </c>
+      <c r="AE4">
         <v>1.33</v>
       </c>
-      <c r="AF3">
+      <c r="AF4">
         <v>1.8</v>
       </c>
-      <c r="AG3">
-        <v>1.91</v>
-      </c>
-      <c r="AH3">
-        <v>5.5</v>
-      </c>
-      <c r="AI3">
-        <v>1.13</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL3">
-        <v>1.2</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>2.2</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.34</v>
-      </c>
-      <c r="AQ3">
-        <v>1.65</v>
-      </c>
-      <c r="AR3">
-        <v>2.06</v>
-      </c>
-      <c r="AS3">
-        <v>2.7</v>
-      </c>
-      <c r="AT3">
-        <v>3.78</v>
-      </c>
-      <c r="AU3">
-        <v>2.84</v>
-      </c>
-      <c r="AV3">
-        <v>2.11</v>
-      </c>
-      <c r="AW3">
-        <v>1.68</v>
-      </c>
-      <c r="AX3">
-        <v>1.38</v>
-      </c>
-      <c r="AY3">
-        <v>1.18</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.44</v>
-      </c>
-      <c r="BC3">
-        <v>3.1</v>
-      </c>
-      <c r="BD3" s="3">
+      <c r="AG4">
+        <v>1.85</v>
+      </c>
+      <c r="AH4">
+        <v>5.8</v>
+      </c>
+      <c r="AI4">
+        <v>1.09</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45839.66666666666</v>
       </c>
     </row>

--- a/jogos_2025-07-01.xlsx
+++ b/jogos_2025-07-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S3" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.25</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['41', '37', '45+1', '51', '80', '64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['16', '47']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG3" t="n">
         <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.51</v>
+        <v>2.46</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.8</v>
+        <v>1.56</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45839.5</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>5.11</v>
       </c>
       <c r="O4" t="n">
-        <v>3.95</v>
+        <v>2.17</v>
       </c>
       <c r="P4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD4" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '37', '45+1', '51', '80', '64']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['16', '47']</t>
         </is>
       </c>
       <c r="AG4" t="n">
         <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.46</v>
+        <v>1.51</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45839.5</v>
